--- a/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Game\Git\TEngine_main\Configs\GameConfig\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6825050-48E9-4AAB-B186-D977852CECCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="15380"/>
+    <workbookView xWindow="28815" yWindow="15" windowWidth="28770" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -209,14 +215,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -228,6 +228,7 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -235,141 +236,27 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -388,182 +275,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -571,170 +284,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -743,87 +295,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="23" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -832,65 +309,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="22" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="3">
+    <cellStyle name="差" xfId="2" builtinId="27"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="好" xfId="1" builtinId="26"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1148,23 +586,23 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="20.625" customWidth="1"/>
     <col min="5" max="6" width="12.25" customWidth="1"/>
     <col min="7" max="9" width="15" customWidth="1"/>
-    <col min="10" max="12" width="13.5089285714286" customWidth="1"/>
-    <col min="13" max="13" width="10.3839285714286" customWidth="1"/>
+    <col min="10" max="12" width="13.5" customWidth="1"/>
+    <col min="13" max="13" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1192,17 +630,17 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1228,7 +666,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1257,7 +695,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="2:14">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A4" s="4"/>
       <c r="B4" s="2" t="s">
         <v>22</v>
       </c>
@@ -1276,7 +715,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="10:14">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A5" s="4"/>
       <c r="J5" s="2" t="s">
         <v>27</v>
       </c>
@@ -1288,7 +728,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="2:14">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A6" s="4"/>
       <c r="B6" s="2" t="s">
         <v>29</v>
       </c>
@@ -1305,7 +746,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="10:14">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A7" s="4"/>
       <c r="J7" t="s">
         <v>33</v>
       </c>
@@ -1316,7 +758,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="10:14">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A8" s="4"/>
       <c r="J8" t="s">
         <v>36</v>
       </c>
@@ -1327,7 +770,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="10:14">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A9" s="4"/>
       <c r="J9" t="s">
         <v>38</v>
       </c>
@@ -1338,7 +782,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="2:14">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A10" s="4"/>
       <c r="B10" t="s">
         <v>41</v>
       </c>
@@ -1355,7 +800,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="10:14">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A11" s="4"/>
       <c r="J11" t="s">
         <v>43</v>
       </c>
@@ -1366,7 +812,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="10:14">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A12" s="4"/>
       <c r="J12" t="s">
         <v>44</v>
       </c>
@@ -1377,7 +824,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="2:14">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A13" s="4"/>
       <c r="B13" s="3" t="s">
         <v>45</v>
       </c>
@@ -1394,7 +842,8 @@
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
     </row>
-    <row r="14" spans="2:14">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A14" s="4"/>
       <c r="B14" s="3" t="s">
         <v>46</v>
       </c>
@@ -1423,7 +872,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="2:14">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A15" s="4"/>
       <c r="B15" s="3" t="s">
         <v>52</v>
       </c>
@@ -1452,7 +902,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="2:14">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A16" s="4"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -1477,8 +928,8 @@
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/Configs/GameConfig/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Game\Git\TEngine_main\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6825050-48E9-4AAB-B186-D977852CECCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AEE584-E93B-4C2A-B8D9-444DB342683B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28815" yWindow="15" windowWidth="28770" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="66">
   <si>
     <t>##var</t>
   </si>
@@ -210,6 +210,34 @@
   </si>
   <si>
     <t>高度</t>
+  </si>
+  <si>
+    <t>level</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>等级</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>price</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>价格</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>chapter.ChapterItemLevel</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>,</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -296,7 +324,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -309,11 +337,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -592,10 +623,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="4" width="20.625" customWidth="1"/>
+    <col min="2" max="2" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="20.625" customWidth="1"/>
     <col min="5" max="6" width="12.25" customWidth="1"/>
     <col min="7" max="9" width="15" customWidth="1"/>
     <col min="10" max="12" width="13.5" customWidth="1"/>
@@ -696,7 +728,9 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A4" s="4"/>
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
       <c r="B4" s="2" t="s">
         <v>22</v>
       </c>
@@ -716,7 +750,9 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A5" s="4"/>
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
       <c r="J5" s="2" t="s">
         <v>27</v>
       </c>
@@ -729,7 +765,9 @@
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A6" s="4"/>
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
       <c r="B6" s="2" t="s">
         <v>29</v>
       </c>
@@ -747,7 +785,9 @@
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A7" s="4"/>
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
       <c r="J7" t="s">
         <v>33</v>
       </c>
@@ -759,7 +799,9 @@
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A8" s="4"/>
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
       <c r="J8" t="s">
         <v>36</v>
       </c>
@@ -771,7 +813,9 @@
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A9" s="4"/>
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
       <c r="J9" t="s">
         <v>38</v>
       </c>
@@ -783,7 +827,9 @@
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A10" s="4"/>
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
       <c r="B10" t="s">
         <v>41</v>
       </c>
@@ -801,7 +847,9 @@
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A11" s="4"/>
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
       <c r="J11" t="s">
         <v>43</v>
       </c>
@@ -813,7 +861,9 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A12" s="4"/>
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
       <c r="J12" t="s">
         <v>44</v>
       </c>
@@ -825,7 +875,9 @@
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A13" s="4"/>
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
       <c r="B13" s="3" t="s">
         <v>45</v>
       </c>
@@ -843,7 +895,9 @@
       <c r="N13" s="3"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A14" s="4"/>
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
       <c r="B14" s="3" t="s">
         <v>46</v>
       </c>
@@ -873,7 +927,9 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A15" s="4"/>
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
       <c r="B15" s="3" t="s">
         <v>52</v>
       </c>
@@ -903,7 +959,9 @@
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A16" s="4"/>
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -924,6 +982,34 @@
         <v>58</v>
       </c>
     </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B17" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="J18" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>

--- a/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/Configs/GameConfig/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Game\Git\TEngine_main\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AEE584-E93B-4C2A-B8D9-444DB342683B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE5EAF84-9B9C-4EFA-8B95-F38783759BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="68">
   <si>
     <t>##var</t>
   </si>
@@ -77,30 +77,6 @@
     <t>##</t>
   </si>
   <si>
-    <t>全名(包含模块和名字)</t>
-  </si>
-  <si>
-    <t>分割符</t>
-  </si>
-  <si>
-    <t>字段名</t>
-  </si>
-  <si>
-    <t>字段别名</t>
-  </si>
-  <si>
-    <t>类型</t>
-  </si>
-  <si>
-    <t>分组</t>
-  </si>
-  <si>
-    <t>注释</t>
-  </si>
-  <si>
-    <t>字段变体</t>
-  </si>
-  <si>
     <t>item.ItemExchange</t>
   </si>
   <si>
@@ -113,51 +89,30 @@
     <t>int</t>
   </si>
   <si>
-    <t>道具id</t>
-  </si>
-  <si>
     <t>num</t>
   </si>
   <si>
-    <t>道具数量</t>
-  </si>
-  <si>
     <t>test.TestExcelBean1</t>
   </si>
   <si>
-    <t>这是个测试excel结构</t>
-  </si>
-  <si>
     <t>x1</t>
   </si>
   <si>
-    <t>最高品质</t>
-  </si>
-  <si>
     <t>x2</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
-    <t>黑色的</t>
-  </si>
-  <si>
     <t>x3</t>
   </si>
   <si>
-    <t>蓝色的</t>
-  </si>
-  <si>
     <t>x4</t>
   </si>
   <si>
     <t>float</t>
   </si>
   <si>
-    <t>最差品质</t>
-  </si>
-  <si>
     <t>test.TestExcelBean2</t>
   </si>
   <si>
@@ -179,72 +134,406 @@
     <t>Shape</t>
   </si>
   <si>
-    <t>圆</t>
-  </si>
-  <si>
-    <t>这是一个圆</t>
-  </si>
-  <si>
     <t>radius</t>
   </si>
   <si>
-    <t>半径</t>
-  </si>
-  <si>
     <t>test.Rectangle</t>
   </si>
   <si>
-    <t>矩形</t>
-  </si>
-  <si>
-    <t>这是一个矩形</t>
-  </si>
-  <si>
     <t>width</t>
   </si>
   <si>
-    <t>宽度</t>
-  </si>
-  <si>
     <t>height</t>
   </si>
   <si>
-    <t>高度</t>
-  </si>
-  <si>
     <t>level</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>等级</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>price</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>价格</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>chapter.ChapterItemLevel</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>,</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>exp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>等级</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>价格</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>经验</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>分割符</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>字段名</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>字段别名</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>类型</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>分组</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>注释</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>字段变体</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>道具数量</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最高品质</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>黑色的</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>蓝色的</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最差品质</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>圆</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这是一个圆</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>半径</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>矩形</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这是一个矩形</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>宽度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>高度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>全名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="JetBrains Mono ExtraBold"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>包含模块和名字</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="JetBrains Mono ExtraBold"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>道具</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="JetBrains Mono ExtraBold"/>
+        <family val="3"/>
+      </rPr>
+      <t>id</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这是个测试</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="JetBrains Mono ExtraBold"/>
+        <family val="3"/>
+      </rPr>
+      <t>excel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>结构</t>
+    </r>
+  </si>
+  <si>
+    <t>chapter.EntityDetail</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -269,22 +558,39 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="JetBrains Mono ExtraBold"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="华文新魏"/>
       <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF9C0006"/>
+      <name val="JetBrains Mono ExtraBold"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF006100"/>
+      <name val="JetBrains Mono ExtraBold"/>
+      <family val="3"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -303,13 +609,34 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -328,22 +655,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -623,399 +950,579 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="20.625" customWidth="1"/>
-    <col min="5" max="6" width="12.25" customWidth="1"/>
-    <col min="7" max="9" width="15" customWidth="1"/>
-    <col min="10" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="10.375" customWidth="1"/>
+    <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+    </row>
+    <row r="2" spans="1:16" ht="21" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="J2" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" spans="1:16" ht="21" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="21" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="J3" t="s">
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="K3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M3" t="s">
-        <v>19</v>
-      </c>
-      <c r="N3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="J4" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
-        <v>25</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="M4" s="2"/>
       <c r="N4" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+        <v>65</v>
+      </c>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+    </row>
+    <row r="5" spans="1:16" ht="21" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
       <c r="J5" s="2" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+    </row>
+    <row r="6" spans="1:16" ht="21" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+    </row>
+    <row r="7" spans="1:16" ht="21" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" ht="21" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+    </row>
+    <row r="9" spans="1:16" ht="21" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="M9" s="2"/>
+      <c r="N9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+    </row>
+    <row r="10" spans="1:16" ht="21" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+    </row>
+    <row r="11" spans="1:16" ht="21" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="K11" s="2"/>
+      <c r="L11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+    </row>
+    <row r="12" spans="1:16" ht="21" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G6" t="s">
+      <c r="K12" s="2"/>
+      <c r="L12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+    </row>
+    <row r="13" spans="1:16" ht="21" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J6" t="s">
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+    </row>
+    <row r="14" spans="1:16" ht="21" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L6" t="s">
+      <c r="C14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="N6" t="s">
+      <c r="M14" s="1"/>
+      <c r="N14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+    </row>
+    <row r="15" spans="1:16" ht="21" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+    </row>
+    <row r="16" spans="1:16" ht="21" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J7" t="s">
-        <v>33</v>
-      </c>
-      <c r="L7" t="s">
-        <v>34</v>
-      </c>
-      <c r="N7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J8" t="s">
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="L8" t="s">
+      <c r="K16" s="1"/>
+      <c r="L16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="N8" t="s">
+      <c r="M16" s="1"/>
+      <c r="N16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+    </row>
+    <row r="17" spans="1:16" ht="21" x14ac:dyDescent="0.2">
+      <c r="A17" s="2"/>
+      <c r="B17" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="5" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="K17" s="6"/>
+      <c r="L17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M17" s="6"/>
+      <c r="N17" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+    </row>
+    <row r="18" spans="1:16" ht="21" x14ac:dyDescent="0.2">
+      <c r="A18" s="2"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="N9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="K18" s="6"/>
+      <c r="L18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M18" s="6"/>
+      <c r="N18" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+    </row>
+    <row r="19" spans="1:16" ht="21" x14ac:dyDescent="0.2">
+      <c r="A19" s="2"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G10" t="s">
-        <v>30</v>
-      </c>
-      <c r="J10" t="s">
-        <v>42</v>
-      </c>
-      <c r="L10" t="s">
-        <v>25</v>
-      </c>
-      <c r="N10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="J11" t="s">
-        <v>43</v>
-      </c>
-      <c r="L11" t="s">
-        <v>34</v>
-      </c>
-      <c r="N11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="K19" s="6"/>
+      <c r="L19" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M19" s="6"/>
+      <c r="N19" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="L12" t="s">
-        <v>39</v>
-      </c>
-      <c r="N12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B17" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="J18" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>